--- a/CO国試data/CO_questions_2025.xlsx
+++ b/CO国試data/CO_questions_2025.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -638,12 +637,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>健康、疾病、障害の概念</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>False</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1010,12 +1005,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>健康、疾病、障害の概念</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1289,12 +1281,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1382,12 +1373,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>健康、疾病、障害の概念</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>3</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1565,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1622,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1658,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -1715,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1751,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1808,7 +1795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1844,15 +1830,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1901,7 +1887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1937,15 +1922,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -1994,7 +1979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>True</t>
@@ -2030,15 +2014,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2128,15 +2112,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -2226,15 +2210,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2283,7 +2267,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>True</t>
@@ -2319,15 +2302,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -2376,7 +2359,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2415,12 +2397,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2469,7 +2451,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>True</t>
@@ -2505,15 +2486,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -2562,7 +2543,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2598,15 +2578,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>1</v>
       </c>
@@ -2655,7 +2635,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2691,15 +2670,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -2748,7 +2727,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2784,15 +2762,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -2841,7 +2819,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2877,15 +2854,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2975,15 +2952,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>1</v>
       </c>
@@ -3032,7 +3009,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3068,15 +3044,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>3</v>
       </c>
@@ -3125,7 +3101,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>True</t>
@@ -3164,12 +3139,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>1</v>
       </c>
@@ -3218,7 +3193,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3254,15 +3228,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>1</v>
       </c>
@@ -3352,15 +3326,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3450,15 +3424,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>1</v>
       </c>
@@ -3507,7 +3481,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3543,15 +3516,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>1</v>
       </c>
@@ -3600,7 +3573,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3636,15 +3608,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3693,7 +3665,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3729,15 +3700,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -3786,7 +3757,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3822,15 +3792,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>1</v>
       </c>
@@ -3879,7 +3849,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3915,15 +3884,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3972,7 +3941,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -4008,15 +3976,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4065,7 +4033,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4101,15 +4068,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4199,15 +4166,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4256,7 +4223,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4292,15 +4258,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>1</v>
       </c>
@@ -4349,7 +4315,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>False</t>
@@ -4385,15 +4350,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4442,7 +4407,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>True</t>
@@ -4478,15 +4442,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4535,7 +4499,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>True</t>
@@ -4571,15 +4534,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>1</v>
       </c>
@@ -4628,7 +4591,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4664,15 +4626,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>1</v>
       </c>
@@ -4721,7 +4683,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4757,15 +4718,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>1</v>
       </c>
@@ -4814,7 +4775,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4850,15 +4810,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -4907,7 +4867,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4943,15 +4902,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -5000,7 +4959,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>True</t>
@@ -5036,15 +4994,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>1</v>
       </c>
@@ -5093,7 +5051,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5129,15 +5086,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>1</v>
       </c>
@@ -5186,7 +5143,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5222,15 +5178,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5279,7 +5235,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>True</t>
@@ -5315,15 +5270,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>1</v>
       </c>
@@ -5372,7 +5327,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>False</t>
@@ -5408,15 +5362,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>1</v>
       </c>
@@ -5465,7 +5419,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5501,15 +5454,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5558,7 +5511,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>True</t>
@@ -5594,15 +5546,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>1</v>
       </c>
@@ -5651,7 +5603,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5687,15 +5638,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5744,7 +5695,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>True</t>
@@ -5780,15 +5730,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>1</v>
       </c>
@@ -5837,7 +5787,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5873,15 +5822,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5930,7 +5879,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>False</t>
@@ -5966,15 +5914,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -6023,7 +5971,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6059,15 +6006,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>1</v>
       </c>
@@ -6116,7 +6063,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6152,15 +6098,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>1</v>
       </c>
@@ -6209,7 +6155,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6245,15 +6190,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>1</v>
       </c>
@@ -6302,7 +6247,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6338,15 +6282,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>1</v>
       </c>
@@ -6395,7 +6339,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6431,15 +6374,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>1</v>
       </c>
@@ -6488,7 +6431,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6524,15 +6466,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>1</v>
       </c>
@@ -6581,7 +6523,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6617,15 +6558,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6715,15 +6656,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>5</v>
       </c>
@@ -6813,15 +6754,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -6871,7 +6812,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>False</t>
@@ -6907,15 +6847,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -7005,15 +6945,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7063,7 +7003,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
           <t>True</t>
@@ -7099,15 +7038,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7197,15 +7136,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7295,15 +7234,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7353,7 +7292,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>False</t>
@@ -7389,15 +7327,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7487,15 +7425,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7585,15 +7523,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7642,7 +7580,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7678,15 +7615,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7735,7 +7672,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7771,15 +7707,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7828,7 +7764,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7864,15 +7799,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>1</v>
       </c>
@@ -7921,7 +7856,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7957,15 +7891,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -8014,7 +7948,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8050,15 +7983,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -8107,7 +8040,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8143,15 +8075,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>1</v>
       </c>
@@ -8200,7 +8132,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8239,12 +8170,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8293,7 +8224,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8329,15 +8259,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8386,7 +8316,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8422,15 +8351,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>3</v>
       </c>
@@ -8520,15 +8449,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>1</v>
       </c>
@@ -8577,7 +8506,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8613,15 +8541,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>1</v>
       </c>
@@ -8670,7 +8598,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8706,15 +8633,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>2</v>
       </c>
@@ -8804,15 +8731,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8861,7 +8788,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8897,15 +8823,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>1</v>
       </c>
@@ -8954,7 +8880,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8990,15 +8915,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>1</v>
       </c>
@@ -9047,7 +8972,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9083,15 +9007,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9140,7 +9064,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9176,15 +9099,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>1</v>
       </c>
@@ -9233,7 +9156,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9269,15 +9191,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9327,7 +9249,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9363,15 +9284,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>1</v>
       </c>
@@ -9420,7 +9341,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9456,15 +9376,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>1</v>
       </c>
@@ -9513,7 +9433,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9549,15 +9468,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>2</v>
       </c>
@@ -9606,7 +9525,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>False</t>
@@ -9642,15 +9560,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9699,7 +9617,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9735,15 +9652,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9833,15 +9750,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9890,7 +9807,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>True</t>
@@ -9926,15 +9842,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -10024,15 +9940,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>1</v>
       </c>
@@ -10081,7 +9997,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10117,15 +10032,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>1</v>
       </c>
@@ -10174,7 +10089,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>False</t>
@@ -10210,15 +10124,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10308,15 +10222,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>2</v>
       </c>
@@ -10365,7 +10279,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10401,15 +10314,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>1</v>
       </c>
@@ -10458,7 +10371,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10494,15 +10406,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>1</v>
       </c>
@@ -10551,7 +10463,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10587,15 +10498,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10645,7 +10556,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10681,15 +10591,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>1</v>
       </c>
@@ -10738,7 +10648,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10774,15 +10683,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10831,7 +10740,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10867,15 +10775,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10924,7 +10832,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10960,15 +10867,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>3</v>
       </c>
@@ -11018,7 +10925,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>False</t>
@@ -11057,12 +10963,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11111,7 +11017,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>True</t>
@@ -11147,15 +11052,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>1</v>
       </c>
@@ -11204,7 +11109,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11240,15 +11144,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>3</v>
       </c>
@@ -11297,7 +11201,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>True</t>
@@ -11333,15 +11236,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11390,7 +11293,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>True</t>
@@ -11426,15 +11328,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>1</v>
       </c>
@@ -11483,7 +11385,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11519,15 +11420,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>1</v>
       </c>
@@ -11576,7 +11477,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11612,15 +11512,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>1</v>
       </c>
@@ -11669,7 +11569,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11705,15 +11604,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>1</v>
       </c>
@@ -11762,7 +11661,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11798,15 +11696,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>1</v>
       </c>
@@ -11855,7 +11753,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11891,15 +11788,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11948,7 +11845,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11984,15 +11880,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>1</v>
       </c>
@@ -12041,7 +11937,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12077,15 +11972,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12134,7 +12029,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>True</t>
@@ -12170,15 +12064,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>1</v>
       </c>
@@ -12227,7 +12121,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>False</t>
@@ -12263,15 +12156,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>1</v>
       </c>
@@ -12320,7 +12213,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12356,15 +12248,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>1</v>
       </c>
@@ -12414,7 +12306,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12450,15 +12341,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>2</v>
       </c>
@@ -12507,7 +12398,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12543,15 +12433,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>1</v>
       </c>
@@ -12600,7 +12490,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12636,15 +12525,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>1</v>
       </c>
@@ -12693,7 +12582,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12729,15 +12617,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>1</v>
       </c>
@@ -12786,7 +12674,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>False</t>
@@ -12822,15 +12709,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12879,7 +12766,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>False</t>
@@ -12915,15 +12801,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12973,7 +12859,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -13009,15 +12894,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -13066,7 +12951,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13102,15 +12986,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13159,7 +13043,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>True</t>
@@ -13195,15 +13078,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13252,7 +13135,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>False</t>
@@ -13288,15 +13170,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13345,7 +13227,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>True</t>
@@ -13381,15 +13262,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>1</v>
       </c>
@@ -13438,7 +13319,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13474,15 +13354,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>1</v>
       </c>
@@ -13531,7 +13411,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13567,15 +13446,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>1</v>
       </c>
@@ -13624,7 +13503,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>False</t>
@@ -13660,15 +13538,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>2</v>
       </c>
@@ -13758,15 +13636,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13856,15 +13734,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13954,15 +13832,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>4</v>
       </c>
@@ -14052,15 +13930,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>2</v>
       </c>
@@ -14150,15 +14028,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>5</v>
       </c>
@@ -14208,7 +14086,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
           <t>True</t>
@@ -14244,15 +14121,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>5</v>
       </c>
@@ -14342,15 +14219,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>2</v>
       </c>
@@ -14400,7 +14277,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
           <t>False</t>
@@ -14436,15 +14312,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14534,15 +14410,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2025.xlsx
+++ b/CO国試data/CO_questions_2025.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>健康、疾病、障害の概念</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>健康、疾病、障害の概念</t>
+          <t>健康、疾病、障害の基本的知識</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>健康、疾病、障害の概念</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>健康、疾病、障害の概念</t>
+          <t>健康、疾病、障害の基本的知識</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>健康の指標</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>健康、疾病、障害の概念</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>健康、疾病、障害の概念</t>
+          <t>老年期疾患</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3516,12 +3516,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3976,12 +3976,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4068,12 +4068,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>中心フリッカ検査</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5086,12 +5086,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>屈折異常</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5454,12 +5454,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5638,12 +5638,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5822,12 +5822,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6006,12 +6006,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6282,12 +6282,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6466,12 +6466,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6558,12 +6558,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6847,12 +6847,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7136,12 +7136,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7425,12 +7425,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>中心フリッカ検査</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7615,12 +7615,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7707,12 +7707,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7891,12 +7891,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7983,12 +7983,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8075,12 +8075,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8167,12 +8167,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>リハビリテーションの考え方</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8259,12 +8259,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球の血管系</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8351,12 +8351,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8633,12 +8633,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -9007,12 +9007,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9099,12 +9099,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9191,12 +9191,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9284,12 +9284,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9468,12 +9468,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9652,12 +9652,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -10032,12 +10032,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10222,12 +10222,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>画像検査</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10406,12 +10406,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10498,12 +10498,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10591,12 +10591,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10683,12 +10683,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11052,12 +11052,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11144,12 +11144,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>涙器</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11420,12 +11420,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11512,12 +11512,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11696,12 +11696,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11788,12 +11788,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11972,12 +11972,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12064,12 +12064,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12156,12 +12156,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12248,12 +12248,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12433,12 +12433,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12525,12 +12525,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12617,12 +12617,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12709,12 +12709,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12801,12 +12801,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12894,12 +12894,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12986,12 +12986,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13078,12 +13078,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13262,12 +13262,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13354,12 +13354,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13538,12 +13538,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13636,12 +13636,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13734,12 +13734,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13832,12 +13832,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -14028,12 +14028,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14121,12 +14121,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14219,12 +14219,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14312,12 +14312,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14410,12 +14410,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2025.xlsx
+++ b/CO国試data/CO_questions_2025.xlsx
@@ -550,7 +550,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -642,7 +641,6 @@
           <t>健康、疾病、障害の基本的知識</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -734,7 +732,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -826,7 +823,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -918,7 +914,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1005,6 @@
           <t>健康、疾病、障害の基本的知識</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -1102,7 +1096,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -1194,7 +1192,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>涙液層破壊時間〈BUT〉</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1286,7 +1288,6 @@
           <t>健康の指標</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -1378,7 +1379,11 @@
           <t>老年期疾患</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>加齢と老化、フレイル</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>3</v>
       </c>
@@ -1470,7 +1475,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1562,7 +1571,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1654,7 +1667,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -1746,7 +1763,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1838,7 +1859,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1930,7 +1955,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -2022,7 +2051,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2120,7 +2148,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -2218,7 +2250,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2310,7 +2341,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -2402,7 +2437,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2494,7 +2528,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -2586,7 +2624,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
@@ -2678,7 +2720,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -2770,7 +2816,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -2862,7 +2907,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2960,7 +3009,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>1</v>
       </c>
@@ -3052,7 +3100,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>3</v>
       </c>
@@ -3144,7 +3191,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>1</v>
       </c>
@@ -3236,7 +3282,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>1</v>
       </c>
@@ -3334,7 +3379,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3432,7 +3476,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>局所麻酔薬</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
@@ -3524,7 +3572,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>1</v>
       </c>
@@ -3616,7 +3663,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3708,7 +3754,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>核・核下性〈末梢性〉眼球運動障害〈眼球運動神経麻痺〉</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -3800,7 +3850,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>1</v>
       </c>
@@ -3892,7 +3941,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3984,7 +4032,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4076,7 +4123,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4174,7 +4225,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4266,7 +4321,11 @@
           <t>中心フリッカ検査</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>限界フリッカ値〈CFF〉</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
@@ -4358,7 +4417,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4450,7 +4508,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>斜視弱視</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4542,7 +4604,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
@@ -4634,7 +4700,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
@@ -4726,7 +4796,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>視交叉から後頭葉までの視覚伝導路の疾患</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
@@ -4818,7 +4892,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -4910,7 +4988,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>兎眼</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -5002,7 +5084,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>麦粒腫</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
@@ -5094,7 +5180,6 @@
           <t>屈折異常</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>1</v>
       </c>
@@ -5186,7 +5271,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5278,7 +5362,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>原発閉塞隅角緑内障</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
@@ -5370,7 +5458,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>1</v>
       </c>
@@ -5462,7 +5554,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5554,7 +5650,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>1</v>
       </c>
@@ -5646,7 +5741,11 @@
           <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>眼球運動訓練</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5738,7 +5837,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>1</v>
       </c>
@@ -5830,7 +5933,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5922,7 +6024,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>神経筋接合部障害</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -6014,7 +6120,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>1</v>
       </c>
@@ -6106,7 +6211,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>1</v>
       </c>
@@ -6198,7 +6302,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
@@ -6290,7 +6398,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>1</v>
       </c>
@@ -6382,7 +6489,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>1</v>
       </c>
@@ -6474,7 +6585,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>1</v>
       </c>
@@ -6566,7 +6681,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6664,7 +6783,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>5</v>
       </c>
@@ -6762,7 +6885,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -6855,7 +6982,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -6953,7 +7079,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7046,7 +7176,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>視神経症</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7144,7 +7278,6 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7242,7 +7375,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>対光反射異常</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7335,7 +7472,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7433,7 +7569,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7531,7 +7666,6 @@
           <t>中心フリッカ検査</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7623,7 +7757,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7715,7 +7848,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7807,7 +7939,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>1</v>
       </c>
@@ -7899,7 +8030,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -7991,7 +8121,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -8083,7 +8212,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>1</v>
       </c>
@@ -8175,7 +8303,11 @@
           <t>リハビリテーションの考え方</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ノーマライゼーション</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8267,7 +8399,11 @@
           <t>眼球の血管系</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>海綿静脈洞</t>
+        </is>
+      </c>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8359,7 +8495,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>3</v>
       </c>
@@ -8457,7 +8592,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>1</v>
       </c>
@@ -8549,7 +8683,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>1</v>
       </c>
@@ -8641,7 +8774,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>2</v>
       </c>
@@ -8739,7 +8876,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8831,7 +8967,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>1</v>
       </c>
@@ -8923,7 +9058,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>1</v>
       </c>
@@ -9015,7 +9149,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>遠視</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9107,7 +9245,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>1</v>
       </c>
@@ -9199,7 +9336,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9292,7 +9433,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>1</v>
       </c>
@@ -9384,7 +9529,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>1</v>
       </c>
@@ -9476,7 +9620,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>2</v>
       </c>
@@ -9568,7 +9711,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9660,7 +9802,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9758,7 +9899,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9850,7 +9990,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -9948,7 +10092,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>1</v>
       </c>
@@ -10040,7 +10183,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>1</v>
       </c>
@@ -10132,7 +10279,11 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>倒像、直像鏡検査</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10230,7 +10381,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>2</v>
       </c>
@@ -10322,7 +10472,11 @@
           <t>画像検査</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>超音波検査</t>
+        </is>
+      </c>
       <c r="H107" t="n">
         <v>1</v>
       </c>
@@ -10414,7 +10568,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>1</v>
       </c>
@@ -10506,7 +10659,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10599,7 +10751,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>1</v>
       </c>
@@ -10691,7 +10842,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>微小斜視</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10783,7 +10938,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10875,7 +11034,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>3</v>
       </c>
@@ -10968,7 +11126,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11060,7 +11217,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>1</v>
       </c>
@@ -11152,7 +11313,11 @@
           <t>涙器</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>涙液分泌減少症、眼乾燥症〈ドライアイ〉</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>3</v>
       </c>
@@ -11244,7 +11409,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11336,7 +11500,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>角膜変性（症）、角膜ジストロフィ</t>
+        </is>
+      </c>
       <c r="H118" t="n">
         <v>1</v>
       </c>
@@ -11428,7 +11596,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H119" t="n">
         <v>1</v>
       </c>
@@ -11520,7 +11692,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>1</v>
       </c>
@@ -11612,7 +11783,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>小児緑内障</t>
+        </is>
+      </c>
       <c r="H121" t="n">
         <v>1</v>
       </c>
@@ -11704,7 +11879,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>屈折異常弱視</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>1</v>
       </c>
@@ -11796,7 +11975,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11888,7 +12066,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>1</v>
       </c>
@@ -11980,7 +12157,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12072,7 +12248,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>1</v>
       </c>
@@ -12164,7 +12344,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>1</v>
       </c>
@@ -12256,7 +12435,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>1</v>
       </c>
@@ -12349,7 +12532,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>2</v>
       </c>
@@ -12441,7 +12628,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>1</v>
       </c>
@@ -12533,7 +12724,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>1</v>
       </c>
@@ -12625,7 +12815,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>1</v>
       </c>
@@ -12717,7 +12906,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12809,7 +13002,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12902,7 +13099,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -12994,7 +13195,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13086,7 +13286,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13178,7 +13377,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13270,7 +13468,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>1</v>
       </c>
@@ -13362,7 +13559,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>1</v>
       </c>
@@ -13454,7 +13650,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>1</v>
       </c>
@@ -13546,7 +13746,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>2</v>
       </c>
@@ -13644,7 +13848,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13742,7 +13950,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13840,7 +14052,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H145" t="n">
         <v>4</v>
       </c>
@@ -13938,7 +14154,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>2</v>
       </c>
@@ -14036,7 +14251,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>5</v>
       </c>
@@ -14129,7 +14348,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>5</v>
       </c>
@@ -14227,7 +14445,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>2</v>
       </c>
@@ -14320,7 +14537,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14418,7 +14639,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2025.xlsx
+++ b/CO国試data/CO_questions_2025.xlsx
@@ -598,10 +598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -689,10 +687,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -780,10 +776,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -871,10 +865,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -962,10 +954,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1053,10 +1043,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1149,10 +1137,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1245,10 +1231,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1336,10 +1320,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1528,10 +1510,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1624,10 +1604,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1720,10 +1698,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1816,10 +1792,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1912,10 +1886,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2105,10 +2077,8 @@
           <t>2025_co_25_am017.jpg</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2207,10 +2177,8 @@
           <t>2025_co_25_am018.jpg</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2298,10 +2266,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2394,10 +2360,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2581,10 +2545,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2677,10 +2639,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2773,10 +2733,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2864,10 +2822,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2966,10 +2922,8 @@
           <t>2025_co_25_am026.jpg</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3057,10 +3011,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3239,10 +3191,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3336,10 +3286,8 @@
           <t>2025_co_25_am030.jpg</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3433,10 +3381,8 @@
           <t>2025_co_25_am031.jpg</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3529,10 +3475,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3620,10 +3564,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3711,10 +3653,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3807,10 +3747,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3898,10 +3836,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3989,10 +3925,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4080,10 +4014,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4278,10 +4210,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4374,10 +4304,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4657,10 +4585,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4753,10 +4679,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4849,10 +4773,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4945,10 +4867,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5137,10 +5057,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5228,10 +5146,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5415,10 +5331,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5511,10 +5425,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5698,10 +5610,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5890,10 +5800,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5981,10 +5889,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6077,10 +5983,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6168,10 +6072,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6259,10 +6161,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6355,10 +6255,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6446,10 +6344,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6542,10 +6438,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6638,10 +6532,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6740,10 +6632,8 @@
           <t>2025_co_25_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6842,10 +6732,8 @@
           <t>2025_co_25_am067.jpg</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6939,10 +6827,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7036,10 +6922,8 @@
           <t>2025_co_25_am069.jpg</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7235,10 +7119,8 @@
           <t>2025_co_25_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7332,10 +7214,8 @@
           <t>2025_co_25_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7429,10 +7309,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7526,10 +7404,8 @@
           <t>2025_co_25_am074.jpg</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7623,10 +7499,8 @@
           <t>2025_co_25_am075.jpg</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7714,10 +7588,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7805,10 +7677,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7896,10 +7766,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7987,10 +7855,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8078,10 +7944,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8169,10 +8033,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8260,10 +8122,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8356,10 +8216,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8452,10 +8310,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8549,10 +8405,8 @@
           <t>2025_co_25_pm010.jpg</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8640,10 +8494,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8731,10 +8583,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8833,10 +8683,8 @@
           <t>2025_co_25_pm013.jpg</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8924,10 +8772,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9015,10 +8861,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9106,10 +8950,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9202,10 +9044,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9293,10 +9133,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9390,10 +9228,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9486,10 +9322,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9577,10 +9411,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9668,10 +9500,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9759,10 +9589,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9856,10 +9684,8 @@
           <t>2025_co_25_pm024.jpg</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10049,10 +9875,8 @@
           <t>2025_co_25_pm026.jpg</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10140,10 +9964,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10236,10 +10058,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S104" t="b">
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10338,10 +10158,8 @@
           <t>2025_co_25_pm029.jpg</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10429,10 +10247,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10525,10 +10341,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10616,10 +10430,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10708,10 +10520,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10799,10 +10609,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10895,10 +10703,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -10991,10 +10797,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11083,10 +10887,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11270,10 +11072,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11553,10 +11353,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11649,10 +11447,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11740,10 +11536,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11836,10 +11630,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11932,10 +11724,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12023,10 +11813,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12114,10 +11902,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12205,10 +11991,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12301,10 +12085,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S126" t="b">
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12392,10 +12174,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12489,10 +12269,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12585,10 +12363,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12681,10 +12457,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12772,10 +12546,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12863,10 +12635,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -12959,10 +12729,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13056,10 +12824,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13152,10 +12918,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13334,10 +13098,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13516,10 +13278,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13607,10 +13367,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13703,10 +13461,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13805,10 +13561,8 @@
           <t>2025_co_25_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13907,10 +13661,8 @@
           <t>2025_co_25_pm067.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14009,10 +13761,8 @@
           <t>2025_co_25_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14111,10 +13861,8 @@
           <t>2025_co_25_pm069.jpg</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14208,10 +13956,8 @@
           <t>2025_co_25_pm070.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14494,10 +14240,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14596,10 +14340,8 @@
           <t>2025_co_25_pm074.jpg</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14698,10 +14440,8 @@
           <t>2025_co_25_pm075.jpg</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2025.xlsx
+++ b/CO国試data/CO_questions_2025.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="S2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1414,10 +1414,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S11" t="b">
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1967,7 +1965,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1980,10 +1978,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S17" t="b">
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,7 +2432,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2449,10 +2445,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S22" t="b">
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,7 +3081,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3100,10 +3094,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S29" t="b">
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3912,7 +3904,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3926,7 +3918,7 @@
         </is>
       </c>
       <c r="S38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4096,7 +4088,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4114,10 +4106,8 @@
           <t>2025_co_25_am039.jpg</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S40" t="b">
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4380,7 +4370,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4393,10 +4383,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S43" t="b">
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4476,7 +4464,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4489,10 +4477,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S44" t="b">
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4948,7 +4934,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4961,10 +4947,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S49" t="b">
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5222,7 +5206,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5235,10 +5219,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S52" t="b">
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5506,7 +5488,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5519,10 +5501,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S55" t="b">
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5691,7 +5671,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5704,10 +5684,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S57" t="b">
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7004,7 +6982,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7017,10 +6995,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S71" t="b">
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9760,7 +9736,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9773,10 +9749,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S101" t="b">
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10963,7 +10937,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10976,10 +10950,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S114" t="b">
+        <v>1</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11153,7 +11125,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -11166,10 +11138,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S116" t="b">
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11244,7 +11214,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -11257,10 +11227,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S117" t="b">
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12994,7 +12962,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -13007,10 +12975,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S136" t="b">
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13174,7 +13140,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -13187,10 +13153,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S138" t="b">
+        <v>1</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14038,7 +14002,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -14051,10 +14015,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S147" t="b">
+        <v>1</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14130,7 +14092,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -14148,10 +14110,8 @@
           <t>2025_co_25_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S148" t="b">
+        <v>1</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
